--- a/kredi mevduat/kredi_mevduat.xlsx
+++ b/kredi mevduat/kredi_mevduat.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H602"/>
+  <dimension ref="A1:H603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16090,6 +16090,32 @@
       </c>
       <c r="H602" t="n">
         <v>8.039999999999999</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B603" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="C603" t="n">
+        <v>46.17</v>
+      </c>
+      <c r="D603" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="E603" t="n">
+        <v>53.46</v>
+      </c>
+      <c r="F603" t="n">
+        <v>63.67</v>
+      </c>
+      <c r="G603" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="H603" t="n">
+        <v>8.220000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -16103,7 +16129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K602"/>
+  <dimension ref="A1:K603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37196,6 +37222,41 @@
       </c>
       <c r="K602" t="n">
         <v>2.19</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B603" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="C603" t="n">
+        <v>48.27</v>
+      </c>
+      <c r="D603" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="E603" t="n">
+        <v>43.31</v>
+      </c>
+      <c r="F603" t="n">
+        <v>40.08</v>
+      </c>
+      <c r="G603" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="H603" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I603" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J603" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="K603" t="n">
+        <v>2.13</v>
       </c>
     </row>
   </sheetData>

--- a/kredi mevduat/kredi_mevduat.xlsx
+++ b/kredi mevduat/kredi_mevduat.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H603"/>
+  <dimension ref="A1:H604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16116,6 +16116,32 @@
       </c>
       <c r="H603" t="n">
         <v>8.220000000000001</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B604" t="n">
+        <v>64.98</v>
+      </c>
+      <c r="C604" t="n">
+        <v>47.26</v>
+      </c>
+      <c r="D604" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="E604" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="F604" t="n">
+        <v>63.41</v>
+      </c>
+      <c r="G604" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="H604" t="n">
+        <v>7.95</v>
       </c>
     </row>
   </sheetData>
@@ -16129,7 +16155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K603"/>
+  <dimension ref="A1:K604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37257,6 +37283,41 @@
       </c>
       <c r="K603" t="n">
         <v>2.13</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B604" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="C604" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="D604" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="E604" t="n">
+        <v>43.26</v>
+      </c>
+      <c r="F604" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="G604" t="n">
+        <v>46.72</v>
+      </c>
+      <c r="H604" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="I604" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="J604" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="K604" t="n">
+        <v>2.49</v>
       </c>
     </row>
   </sheetData>

--- a/kredi mevduat/kredi_mevduat.xlsx
+++ b/kredi mevduat/kredi_mevduat.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H604"/>
+  <dimension ref="A1:H605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16142,6 +16142,32 @@
       </c>
       <c r="H604" t="n">
         <v>7.95</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B605" t="n">
+        <v>65.16</v>
+      </c>
+      <c r="C605" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="D605" t="n">
+        <v>41.39</v>
+      </c>
+      <c r="E605" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="F605" t="n">
+        <v>63.47</v>
+      </c>
+      <c r="G605" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="H605" t="n">
+        <v>7.92</v>
       </c>
     </row>
   </sheetData>
@@ -16155,7 +16181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K604"/>
+  <dimension ref="A1:K605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37318,6 +37344,41 @@
       </c>
       <c r="K604" t="n">
         <v>2.49</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B605" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="C605" t="n">
+        <v>47.83</v>
+      </c>
+      <c r="D605" t="n">
+        <v>46.52</v>
+      </c>
+      <c r="E605" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="F605" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="G605" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="H605" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I605" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="J605" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="K605" t="n">
+        <v>2.58</v>
       </c>
     </row>
   </sheetData>

--- a/kredi mevduat/kredi_mevduat.xlsx
+++ b/kredi mevduat/kredi_mevduat.xlsx
@@ -37392,7 +37392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40997,6 +40997,32 @@
       </c>
       <c r="H138" t="n">
         <v>7.58</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B139" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="C139" t="n">
+        <v>62.23</v>
+      </c>
+      <c r="D139" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="E139" t="n">
+        <v>32.21</v>
+      </c>
+      <c r="F139" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="G139" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H139" t="n">
+        <v>7.61</v>
       </c>
     </row>
   </sheetData>
@@ -41010,7 +41036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I138"/>
+  <dimension ref="A1:I139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45031,6 +45057,35 @@
       </c>
       <c r="I138" t="n">
         <v>2.21</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B139" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C139" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="D139" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="E139" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="F139" t="n">
+        <v>40.32</v>
+      </c>
+      <c r="G139" t="n">
+        <v>37.36</v>
+      </c>
+      <c r="H139" t="n">
+        <v>47.77</v>
+      </c>
+      <c r="I139" t="n">
+        <v>2.28</v>
       </c>
     </row>
   </sheetData>

--- a/kredi mevduat/kredi_mevduat.xlsx
+++ b/kredi mevduat/kredi_mevduat.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H605"/>
+  <dimension ref="A1:H606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16168,6 +16168,32 @@
       </c>
       <c r="H605" t="n">
         <v>7.92</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B606" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="C606" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="D606" t="n">
+        <v>41.84</v>
+      </c>
+      <c r="E606" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F606" t="n">
+        <v>63.35</v>
+      </c>
+      <c r="G606" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H606" t="n">
+        <v>7.81</v>
       </c>
     </row>
   </sheetData>
@@ -16181,7 +16207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K605"/>
+  <dimension ref="A1:K606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37379,6 +37405,41 @@
       </c>
       <c r="K605" t="n">
         <v>2.58</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B606" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="C606" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="D606" t="n">
+        <v>44.78</v>
+      </c>
+      <c r="E606" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="F606" t="n">
+        <v>38.37</v>
+      </c>
+      <c r="G606" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="H606" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I606" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J606" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="K606" t="n">
+        <v>2.68</v>
       </c>
     </row>
   </sheetData>

--- a/kredi mevduat/kredi_mevduat.xlsx
+++ b/kredi mevduat/kredi_mevduat.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H609"/>
+  <dimension ref="A1:H610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16272,6 +16272,32 @@
       </c>
       <c r="H609" t="n">
         <v>7.64</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B610" t="n">
+        <v>60.64</v>
+      </c>
+      <c r="C610" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="D610" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="E610" t="n">
+        <v>51.64</v>
+      </c>
+      <c r="F610" t="n">
+        <v>62.35</v>
+      </c>
+      <c r="G610" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="H610" t="n">
+        <v>7.74</v>
       </c>
     </row>
   </sheetData>
@@ -16285,7 +16311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K609"/>
+  <dimension ref="A1:K610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37623,6 +37649,41 @@
       </c>
       <c r="K609" t="n">
         <v>2.66</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B610" t="n">
+        <v>44.81</v>
+      </c>
+      <c r="C610" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="D610" t="n">
+        <v>43.47</v>
+      </c>
+      <c r="E610" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="F610" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="G610" t="n">
+        <v>44.76</v>
+      </c>
+      <c r="H610" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I610" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J610" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K610" t="n">
+        <v>2.75</v>
       </c>
     </row>
   </sheetData>
@@ -37636,7 +37697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41267,6 +41328,32 @@
       </c>
       <c r="H139" t="n">
         <v>7.61</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B140" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="C140" t="n">
+        <v>62.46</v>
+      </c>
+      <c r="D140" t="n">
+        <v>40.37</v>
+      </c>
+      <c r="E140" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="F140" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="G140" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="H140" t="n">
+        <v>7.67</v>
       </c>
     </row>
   </sheetData>
@@ -41280,7 +41367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S139"/>
+  <dimension ref="A1:S140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49520,6 +49607,65 @@
       </c>
       <c r="S139" t="n">
         <v>1.81</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B140" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="C140" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="D140" t="n">
+        <v>47.39</v>
+      </c>
+      <c r="E140" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="F140" t="n">
+        <v>40.54</v>
+      </c>
+      <c r="G140" t="n">
+        <v>37.56</v>
+      </c>
+      <c r="H140" t="n">
+        <v>46.26</v>
+      </c>
+      <c r="I140" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L140" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O140" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P140" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R140" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S140" t="n">
+        <v>1.74</v>
       </c>
     </row>
   </sheetData>
